--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_HALAL FOOD QUALITY UIXÓ BÀSQUET.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_HALAL FOOD QUALITY UIXÓ BÀSQUET.xlsx
@@ -643,13 +643,13 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>17.8238</v>
+        <v>21.1337</v>
       </c>
       <c r="E3" t="n">
-        <v>21.443</v>
+        <v>24.686</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.6193</v>
+        <v>-3.5522</v>
       </c>
       <c r="G3" t="n">
         <v>12.3376</v>
@@ -688,13 +688,13 @@
         <v>11.1787</v>
       </c>
       <c r="S3" t="n">
-        <v>-3.5205</v>
+        <v>-0.2107000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>-2.9123</v>
+        <v>0.3305000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6081000000000001</v>
+        <v>-0.5412</v>
       </c>
       <c r="V3" t="n">
         <v>6.258</v>
@@ -721,13 +721,13 @@
         <v>25</v>
       </c>
       <c r="D4" t="n">
-        <v>7.3131</v>
+        <v>19.1319</v>
       </c>
       <c r="E4" t="n">
-        <v>6.195199999999998</v>
+        <v>12.5577</v>
       </c>
       <c r="F4" t="n">
-        <v>1.117699999999999</v>
+        <v>6.574100000000001</v>
       </c>
       <c r="G4" t="n">
         <v>34.1549</v>
@@ -766,13 +766,13 @@
         <v>49.4794</v>
       </c>
       <c r="S4" t="n">
-        <v>-12.2123</v>
+        <v>-0.3936999999999998</v>
       </c>
       <c r="T4" t="n">
-        <v>-12.4247</v>
+        <v>-6.0624</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2125000000000001</v>
+        <v>5.6689</v>
       </c>
       <c r="V4" t="n">
         <v>15.9745</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. WITSON DEAN</t>
+          <t>C. WHITSON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D5" t="n">
-        <v>6.599399999999999</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>5.2135</v>
+        <v>13.0243</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3857</v>
+        <v>-3.8944</v>
       </c>
       <c r="G5" t="n">
-        <v>10.3206</v>
+        <v>0.7054</v>
       </c>
       <c r="H5" t="n">
-        <v>5.040100000000001</v>
+        <v>-5.2497</v>
       </c>
       <c r="I5" t="n">
-        <v>5.2805</v>
+        <v>5.955200000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>9.183299999999999</v>
+        <v>16.1231</v>
       </c>
       <c r="K5" t="n">
-        <v>6.786799999999999</v>
+        <v>6.349299999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>2.3967</v>
+        <v>9.7737</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1373</v>
+        <v>-15.4174</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.7466</v>
+        <v>-11.5988</v>
       </c>
       <c r="O5" t="n">
-        <v>2.8839</v>
+        <v>-3.8185</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.6652</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.7647</v>
+        <v>-17.7762</v>
       </c>
       <c r="R5" t="n">
-        <v>4.764699999999999</v>
+        <v>21.441</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.8209</v>
+        <v>-1.9596</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.1055</v>
+        <v>-2.4791</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7153</v>
+        <v>0.5192999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.9005</v>
+        <v>6.719200000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>1.9005</v>
+        <v>17.1563</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.8009</v>
+        <v>-10.4369</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. ARNAU BELTRAN</t>
+          <t>C. WITSON DEAN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>3.012200000000001</v>
+        <v>8.5</v>
       </c>
       <c r="E6" t="n">
-        <v>-6.319</v>
+        <v>5.887499999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>9.331300000000001</v>
+        <v>2.6126</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.3286</v>
+        <v>10.3206</v>
       </c>
       <c r="H6" t="n">
-        <v>2.0989</v>
+        <v>5.040100000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.4276</v>
+        <v>5.2805</v>
       </c>
       <c r="J6" t="n">
-        <v>10.4567</v>
+        <v>9.183299999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>13.9116</v>
+        <v>6.786799999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>-3.4554</v>
+        <v>2.3967</v>
       </c>
       <c r="M6" t="n">
-        <v>-11.7853</v>
+        <v>1.1373</v>
       </c>
       <c r="N6" t="n">
-        <v>-11.8128</v>
+        <v>-1.7466</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0275000000000003</v>
+        <v>2.8839</v>
       </c>
       <c r="P6" t="n">
-        <v>6.2308</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-21.4413</v>
+        <v>-4.7647</v>
       </c>
       <c r="R6" t="n">
-        <v>27.672</v>
+        <v>4.764699999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>11.131</v>
+        <v>0.07999999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4544999999999999</v>
+        <v>-0.4317</v>
       </c>
       <c r="U6" t="n">
-        <v>11.5855</v>
+        <v>0.5117</v>
       </c>
       <c r="V6" t="n">
-        <v>-13.0209</v>
+        <v>-1.9005</v>
       </c>
       <c r="W6" t="n">
-        <v>5.1197</v>
+        <v>1.9005</v>
       </c>
       <c r="X6" t="n">
-        <v>-18.1406</v>
+        <v>-3.8009</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. DIAGNE</t>
+          <t>D. IGUAL BAU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>2.290199999999999</v>
+        <v>2.654299999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>3.8285</v>
+        <v>-6.0331</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.5386</v>
+        <v>8.6877</v>
       </c>
       <c r="G7" t="n">
-        <v>-16.2214</v>
+        <v>2.5704</v>
       </c>
       <c r="H7" t="n">
-        <v>-11.7123</v>
+        <v>1.1637</v>
       </c>
       <c r="I7" t="n">
-        <v>-4.5092</v>
+        <v>1.4068</v>
       </c>
       <c r="J7" t="n">
-        <v>20.1924</v>
+        <v>3.1565</v>
       </c>
       <c r="K7" t="n">
-        <v>13.8271</v>
+        <v>1.8449</v>
       </c>
       <c r="L7" t="n">
-        <v>6.3653</v>
+        <v>1.3116</v>
       </c>
       <c r="M7" t="n">
-        <v>-36.4139</v>
+        <v>-0.5861000000000003</v>
       </c>
       <c r="N7" t="n">
-        <v>-25.539</v>
+        <v>-0.6811</v>
       </c>
       <c r="O7" t="n">
-        <v>-10.8747</v>
+        <v>0.09519999999999995</v>
       </c>
       <c r="P7" t="n">
-        <v>-18.5089</v>
+        <v>-1.2828</v>
       </c>
       <c r="Q7" t="n">
-        <v>-60.8415</v>
+        <v>-8.613199999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>42.3324</v>
+        <v>7.3302</v>
       </c>
       <c r="S7" t="n">
-        <v>39.9319</v>
+        <v>0.1849000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>24.9637</v>
+        <v>-1.2205</v>
       </c>
       <c r="U7" t="n">
-        <v>14.9683</v>
+        <v>1.4056</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.9119</v>
+        <v>1.1818</v>
       </c>
       <c r="W7" t="n">
-        <v>19.5137</v>
+        <v>0.6438</v>
       </c>
       <c r="X7" t="n">
-        <v>-22.4255</v>
+        <v>0.5378999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>U. MENDIZABAL CUESTA</t>
+          <t>F. BEKOURI KHADIRA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9999</v>
+        <v>0.6509</v>
       </c>
       <c r="E8" t="n">
-        <v>2.3746</v>
+        <v>1.1148</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3747</v>
+        <v>-0.464</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3684999999999998</v>
+        <v>0.5134</v>
       </c>
       <c r="H8" t="n">
-        <v>1.6957</v>
+        <v>0.8018999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.3272</v>
+        <v>-0.2885</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5014</v>
+        <v>1.0187</v>
       </c>
       <c r="K8" t="n">
-        <v>2.0591</v>
+        <v>1.0187</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5577</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1329</v>
+        <v>-0.5053</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3633</v>
+        <v>-0.2167</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7695</v>
+        <v>-0.2885</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.5498</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3665</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0857</v>
+        <v>0.1374</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2006</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2864</v>
+        <v>0.0413</v>
       </c>
       <c r="V8" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.5889</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. BEKOURI KHADIRA</t>
+          <t>U. MENDIZABAL CUESTA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5299</v>
+        <v>0.6372</v>
       </c>
       <c r="E9" t="n">
-        <v>1.0187</v>
+        <v>2.0862</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4888</v>
+        <v>-1.449</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5134</v>
+        <v>0.3684999999999998</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8018999999999999</v>
+        <v>1.6957</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2885</v>
+        <v>-1.3272</v>
       </c>
       <c r="J9" t="n">
-        <v>1.0187</v>
+        <v>1.5014</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0187</v>
+        <v>2.0591</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.5577</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5053</v>
+        <v>-1.1329</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2167</v>
+        <v>-0.3633</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2885</v>
+        <v>-0.7695</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.3665</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0165</v>
+        <v>-0.4486</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>-0.08790000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0165</v>
+        <v>-0.3607</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.5889</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. WHITSON</t>
+          <t>P. ARNAU BELTRAN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1646999999999985</v>
+        <v>-0.0838000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>9.5204</v>
+        <v>-6.0149</v>
       </c>
       <c r="F10" t="n">
-        <v>-9.355499999999999</v>
+        <v>5.9311</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7054</v>
+        <v>-1.3286</v>
       </c>
       <c r="H10" t="n">
-        <v>-5.2497</v>
+        <v>2.0989</v>
       </c>
       <c r="I10" t="n">
-        <v>5.955200000000001</v>
+        <v>-3.4276</v>
       </c>
       <c r="J10" t="n">
-        <v>16.1231</v>
+        <v>10.4567</v>
       </c>
       <c r="K10" t="n">
-        <v>6.349299999999999</v>
+        <v>13.9116</v>
       </c>
       <c r="L10" t="n">
-        <v>9.7737</v>
+        <v>-3.4554</v>
       </c>
       <c r="M10" t="n">
-        <v>-15.4174</v>
+        <v>-11.7853</v>
       </c>
       <c r="N10" t="n">
-        <v>-11.5988</v>
+        <v>-11.8128</v>
       </c>
       <c r="O10" t="n">
-        <v>-3.8185</v>
+        <v>0.0275000000000003</v>
       </c>
       <c r="P10" t="n">
-        <v>3.6652</v>
+        <v>6.2308</v>
       </c>
       <c r="Q10" t="n">
-        <v>-17.7762</v>
+        <v>-21.4413</v>
       </c>
       <c r="R10" t="n">
-        <v>21.441</v>
+        <v>27.672</v>
       </c>
       <c r="S10" t="n">
-        <v>-10.9248</v>
+        <v>8.034800000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-5.9833</v>
+        <v>-0.1507</v>
       </c>
       <c r="U10" t="n">
-        <v>-4.942</v>
+        <v>8.1852</v>
       </c>
       <c r="V10" t="n">
-        <v>6.719200000000001</v>
+        <v>-13.0209</v>
       </c>
       <c r="W10" t="n">
-        <v>17.1563</v>
+        <v>5.1197</v>
       </c>
       <c r="X10" t="n">
-        <v>-10.4369</v>
+        <v>-18.1406</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. IGUAL BAU</t>
+          <t>M. ABAD MOLINER</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>0.08389999999999985</v>
+        <v>-3.6824</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.6407</v>
+        <v>-4.0366</v>
       </c>
       <c r="F11" t="n">
-        <v>7.7244</v>
+        <v>0.3542999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>2.5704</v>
+        <v>-2.1484</v>
       </c>
       <c r="H11" t="n">
-        <v>1.1637</v>
+        <v>-1.4849</v>
       </c>
       <c r="I11" t="n">
-        <v>1.4068</v>
+        <v>-0.6637</v>
       </c>
       <c r="J11" t="n">
-        <v>3.1565</v>
+        <v>-1.1012</v>
       </c>
       <c r="K11" t="n">
-        <v>1.8449</v>
+        <v>0.1393000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>1.3116</v>
+        <v>-1.2404</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.5861000000000003</v>
+        <v>-1.0474</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6811</v>
+        <v>-1.6241</v>
       </c>
       <c r="O11" t="n">
-        <v>0.09519999999999995</v>
+        <v>0.5767</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.2828</v>
+        <v>-1.8326</v>
       </c>
       <c r="Q11" t="n">
-        <v>-8.613199999999999</v>
+        <v>-3.6652</v>
       </c>
       <c r="R11" t="n">
-        <v>7.3302</v>
+        <v>1.8326</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.3857</v>
+        <v>-1.0306</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.8281</v>
+        <v>-0.5373</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4424</v>
+        <v>-0.4931</v>
       </c>
       <c r="V11" t="n">
-        <v>1.1818</v>
+        <v>1.3293</v>
       </c>
       <c r="W11" t="n">
-        <v>0.6438</v>
+        <v>1.267</v>
       </c>
       <c r="X11" t="n">
-        <v>0.5378999999999999</v>
+        <v>0.0623</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. ABAD MOLINER</t>
+          <t>M. PERAL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.169</v>
+        <v>-4.1616</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.3251</v>
+        <v>4.5503</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1560999999999998</v>
+        <v>-8.7118</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.1484</v>
+        <v>-1.92</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.4849</v>
+        <v>0.8129</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6637</v>
+        <v>-2.733</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.1012</v>
+        <v>12.0951</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1393000000000001</v>
+        <v>12.1975</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.2404</v>
+        <v>-0.1025999999999998</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.0474</v>
+        <v>-14.0152</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.6241</v>
+        <v>-11.3845</v>
       </c>
       <c r="O12" t="n">
-        <v>0.5767</v>
+        <v>-2.6307</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.8326</v>
+        <v>-2.0157</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.6652</v>
+        <v>-12.6447</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8326</v>
+        <v>10.629</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.5173</v>
+        <v>-1.6046</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8259</v>
+        <v>-1.2558</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6915</v>
+        <v>-0.3487000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>1.3293</v>
+        <v>1.3792</v>
       </c>
       <c r="W12" t="n">
-        <v>1.267</v>
+        <v>6.355600000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>0.0623</v>
+        <v>-4.9765</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.4323</v>
+        <v>-6.1627</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.361800000000001</v>
+        <v>-5.2656</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.0704</v>
+        <v>-0.8972</v>
       </c>
       <c r="G13" t="n">
         <v>-2.0263</v>
@@ -1468,13 +1468,13 @@
         <v>0.3665</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.1121</v>
+        <v>-0.8425</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3855</v>
+        <v>-0.2893</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7269000000000001</v>
+        <v>-0.5533</v>
       </c>
       <c r="V13" t="n">
         <v>-1.8278</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. CAMAHORT TORRES</t>
+          <t>A. ALBA GONZALEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D14" t="n">
-        <v>-8.0639</v>
+        <v>-7.130599999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.4399</v>
+        <v>-21.8013</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.6239</v>
+        <v>14.6707</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.3323</v>
+        <v>-11.1851</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.0459</v>
+        <v>-8.569699999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2864</v>
+        <v>-2.6155</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5118000000000004</v>
+        <v>6.327300000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>1.758600000000001</v>
+        <v>7.6216</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.2466</v>
+        <v>-1.2944</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.844</v>
+        <v>-17.5125</v>
       </c>
       <c r="N14" t="n">
-        <v>-3.8042</v>
+        <v>-16.1917</v>
       </c>
       <c r="O14" t="n">
-        <v>0.9603</v>
+        <v>-1.3211</v>
       </c>
       <c r="P14" t="n">
-        <v>0.5497999999999996</v>
+        <v>9.8957</v>
       </c>
       <c r="Q14" t="n">
-        <v>-6.7807</v>
+        <v>-31.8868</v>
       </c>
       <c r="R14" t="n">
-        <v>7.330299999999999</v>
+        <v>41.7827</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.5667</v>
+        <v>-1.7194</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3596</v>
+        <v>-7.5312</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.207</v>
+        <v>5.8121</v>
       </c>
       <c r="V14" t="n">
-        <v>-4.7149</v>
+        <v>-4.1225</v>
       </c>
       <c r="W14" t="n">
-        <v>3.1883</v>
+        <v>11.2891</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.9031</v>
+        <v>-15.4113</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. KEITH CAMARA</t>
+          <t>C. CAMAHORT TORRES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D15" t="n">
-        <v>-9.998799999999999</v>
+        <v>-7.969099999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>-7.092300000000001</v>
+        <v>-4.0853</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.9063</v>
+        <v>-3.8836</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.4129000000000003</v>
+        <v>-2.3323</v>
       </c>
       <c r="H15" t="n">
-        <v>-6.565799999999999</v>
+        <v>-2.0459</v>
       </c>
       <c r="I15" t="n">
-        <v>6.1528</v>
+        <v>-0.2864</v>
       </c>
       <c r="J15" t="n">
-        <v>7.377999999999999</v>
+        <v>0.5118000000000004</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0942</v>
+        <v>1.758600000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>6.2836</v>
+        <v>-1.2466</v>
       </c>
       <c r="M15" t="n">
-        <v>-7.7912</v>
+        <v>-2.844</v>
       </c>
       <c r="N15" t="n">
-        <v>-7.6602</v>
+        <v>-3.8042</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1310999999999997</v>
+        <v>0.9603</v>
       </c>
       <c r="P15" t="n">
-        <v>-3.6652</v>
+        <v>0.5497999999999996</v>
       </c>
       <c r="Q15" t="n">
-        <v>-15.2105</v>
+        <v>-6.7807</v>
       </c>
       <c r="R15" t="n">
-        <v>11.5453</v>
+        <v>7.330299999999999</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.4651</v>
+        <v>-1.4714</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.4826</v>
+        <v>-1.0047</v>
       </c>
       <c r="U15" t="n">
-        <v>0.01709999999999991</v>
+        <v>-0.4669</v>
       </c>
       <c r="V15" t="n">
-        <v>-4.4551</v>
+        <v>-4.7149</v>
       </c>
       <c r="W15" t="n">
-        <v>2.2224</v>
+        <v>3.1883</v>
       </c>
       <c r="X15" t="n">
-        <v>-6.6775</v>
+        <v>-7.9031</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. PERAL</t>
+          <t>D. KEITH CAMARA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D16" t="n">
-        <v>-10.1229</v>
+        <v>-8.020199999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>1.376500000000001</v>
+        <v>-6.720800000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>-11.4993</v>
+        <v>-1.2992</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.92</v>
+        <v>-0.4129000000000003</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8129</v>
+        <v>-6.565799999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.733</v>
+        <v>6.1528</v>
       </c>
       <c r="J16" t="n">
-        <v>12.0951</v>
+        <v>7.377999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>12.1975</v>
+        <v>1.0942</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.1025999999999998</v>
+        <v>6.2836</v>
       </c>
       <c r="M16" t="n">
-        <v>-14.0152</v>
+        <v>-7.7912</v>
       </c>
       <c r="N16" t="n">
-        <v>-11.3845</v>
+        <v>-7.6602</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.6307</v>
+        <v>-0.1310999999999997</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.0157</v>
+        <v>-3.6652</v>
       </c>
       <c r="Q16" t="n">
-        <v>-12.6447</v>
+        <v>-15.2105</v>
       </c>
       <c r="R16" t="n">
-        <v>10.629</v>
+        <v>11.5453</v>
       </c>
       <c r="S16" t="n">
-        <v>-7.5661</v>
+        <v>0.5134000000000002</v>
       </c>
       <c r="T16" t="n">
-        <v>-4.4297</v>
+        <v>-1.1112</v>
       </c>
       <c r="U16" t="n">
-        <v>-3.1365</v>
+        <v>1.6244</v>
       </c>
       <c r="V16" t="n">
-        <v>1.3792</v>
+        <v>-4.4551</v>
       </c>
       <c r="W16" t="n">
-        <v>6.355600000000001</v>
+        <v>2.2224</v>
       </c>
       <c r="X16" t="n">
-        <v>-4.9765</v>
+        <v>-6.6775</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. NEBOT GARCIA</t>
+          <t>R. HOLGADO CUELLAR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D17" t="n">
-        <v>-15.7715</v>
+        <v>-16.1985</v>
       </c>
       <c r="E17" t="n">
-        <v>-7.779199999999999</v>
+        <v>-28.549</v>
       </c>
       <c r="F17" t="n">
-        <v>-7.992500000000001</v>
+        <v>12.3504</v>
       </c>
       <c r="G17" t="n">
-        <v>-7.251100000000001</v>
+        <v>-10.5915</v>
       </c>
       <c r="H17" t="n">
-        <v>-5.8811</v>
+        <v>2.2367</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.3699</v>
+        <v>-12.8282</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.5281</v>
+        <v>-1.871200000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3199999999999998</v>
+        <v>11.8821</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.8481</v>
+        <v>-13.7534</v>
       </c>
       <c r="M17" t="n">
-        <v>-5.7229</v>
+        <v>-8.7203</v>
       </c>
       <c r="N17" t="n">
-        <v>-6.201000000000001</v>
+        <v>-9.6456</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4784</v>
+        <v>0.9250000000000003</v>
       </c>
       <c r="P17" t="n">
-        <v>2.7489</v>
+        <v>-8.613300000000001</v>
       </c>
       <c r="Q17" t="n">
-        <v>-8.979799999999999</v>
+        <v>-36.4682</v>
       </c>
       <c r="R17" t="n">
-        <v>11.7285</v>
+        <v>27.855</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7708</v>
+        <v>-7.3435</v>
       </c>
       <c r="T17" t="n">
-        <v>2.6764</v>
+        <v>-7.0751</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.906</v>
+        <v>-0.2686999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>-12.0405</v>
+        <v>10.3499</v>
       </c>
       <c r="W17" t="n">
-        <v>0.0520000000000001</v>
+        <v>16.8654</v>
       </c>
       <c r="X17" t="n">
-        <v>-12.0925</v>
+        <v>-6.515599999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. ALBA GONZALEZ</t>
+          <t>M. NEBOT GARCIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>21</v>
       </c>
       <c r="D18" t="n">
-        <v>-15.9238</v>
+        <v>-17.1642</v>
       </c>
       <c r="E18" t="n">
-        <v>-28.2605</v>
+        <v>-11.1304</v>
       </c>
       <c r="F18" t="n">
-        <v>12.3367</v>
+        <v>-6.0343</v>
       </c>
       <c r="G18" t="n">
-        <v>-11.1851</v>
+        <v>-7.251100000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>-8.569699999999999</v>
+        <v>-5.8811</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.6155</v>
+        <v>-1.3699</v>
       </c>
       <c r="J18" t="n">
-        <v>6.327300000000001</v>
+        <v>-1.5281</v>
       </c>
       <c r="K18" t="n">
-        <v>7.6216</v>
+        <v>0.3199999999999998</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.2944</v>
+        <v>-1.8481</v>
       </c>
       <c r="M18" t="n">
-        <v>-17.5125</v>
+        <v>-5.7229</v>
       </c>
       <c r="N18" t="n">
-        <v>-16.1917</v>
+        <v>-6.201000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.3211</v>
+        <v>0.4784</v>
       </c>
       <c r="P18" t="n">
-        <v>9.8957</v>
+        <v>2.7489</v>
       </c>
       <c r="Q18" t="n">
-        <v>-31.8868</v>
+        <v>-8.979799999999999</v>
       </c>
       <c r="R18" t="n">
-        <v>41.7827</v>
+        <v>11.7285</v>
       </c>
       <c r="S18" t="n">
-        <v>-10.5123</v>
+        <v>-0.6223000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>-13.9903</v>
+        <v>-0.675</v>
       </c>
       <c r="U18" t="n">
-        <v>3.4782</v>
+        <v>0.05230000000000001</v>
       </c>
       <c r="V18" t="n">
-        <v>-4.1225</v>
+        <v>-12.0405</v>
       </c>
       <c r="W18" t="n">
-        <v>11.2891</v>
+        <v>0.0520000000000001</v>
       </c>
       <c r="X18" t="n">
-        <v>-15.4113</v>
+        <v>-12.0925</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>16</v>
       </c>
       <c r="D19" t="n">
-        <v>-23.1153</v>
+        <v>-18.278</v>
       </c>
       <c r="E19" t="n">
-        <v>-23.926</v>
+        <v>-23.4304</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8106999999999999</v>
+        <v>5.1527</v>
       </c>
       <c r="G19" t="n">
         <v>-22.7655</v>
@@ -1936,13 +1936,13 @@
         <v>21.6245</v>
       </c>
       <c r="S19" t="n">
-        <v>-3.9643</v>
+        <v>0.8734000000000002</v>
       </c>
       <c r="T19" t="n">
-        <v>-2.569</v>
+        <v>-2.0737</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.3952</v>
+        <v>2.9468</v>
       </c>
       <c r="V19" t="n">
         <v>0.3157999999999999</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. ARIJA DE LA PENA</t>
+          <t>E. DIAGNE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,76 +1966,76 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D20" t="n">
-        <v>-24.7462</v>
+        <v>-19.8108</v>
       </c>
       <c r="E20" t="n">
-        <v>-32.5761</v>
+        <v>-14.6022</v>
       </c>
       <c r="F20" t="n">
-        <v>7.830299999999999</v>
+        <v>-5.208600000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>-17.4914</v>
+        <v>-16.2214</v>
       </c>
       <c r="H20" t="n">
-        <v>8.602199999999998</v>
+        <v>-11.7123</v>
       </c>
       <c r="I20" t="n">
-        <v>-26.0942</v>
+        <v>-4.5092</v>
       </c>
       <c r="J20" t="n">
-        <v>19.544</v>
+        <v>20.1924</v>
       </c>
       <c r="K20" t="n">
-        <v>35.3075</v>
+        <v>13.8271</v>
       </c>
       <c r="L20" t="n">
-        <v>-15.7635</v>
+        <v>6.3653</v>
       </c>
       <c r="M20" t="n">
-        <v>-37.0356</v>
+        <v>-36.4139</v>
       </c>
       <c r="N20" t="n">
-        <v>-26.7055</v>
+        <v>-25.539</v>
       </c>
       <c r="O20" t="n">
-        <v>-10.3304</v>
+        <v>-10.8747</v>
       </c>
       <c r="P20" t="n">
-        <v>-17.4095</v>
+        <v>-18.5089</v>
       </c>
       <c r="Q20" t="n">
-        <v>-64.5065</v>
+        <v>-60.8415</v>
       </c>
       <c r="R20" t="n">
-        <v>47.0971</v>
+        <v>42.3324</v>
       </c>
       <c r="S20" t="n">
-        <v>6.1751</v>
+        <v>17.8313</v>
       </c>
       <c r="T20" t="n">
-        <v>-4.9156</v>
+        <v>6.533099999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>11.091</v>
+        <v>11.2984</v>
       </c>
       <c r="V20" t="n">
-        <v>3.979800000000001</v>
+        <v>-2.9119</v>
       </c>
       <c r="W20" t="n">
-        <v>17.3018</v>
+        <v>19.5137</v>
       </c>
       <c r="X20" t="n">
-        <v>-13.3222</v>
+        <v>-22.4255</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. HOLGADO CUELLAR</t>
+          <t>D. ARIJA DE LA PENA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>24</v>
       </c>
       <c r="D21" t="n">
-        <v>-25.908</v>
+        <v>-24.2481</v>
       </c>
       <c r="E21" t="n">
-        <v>-33.7426</v>
+        <v>-30.4434</v>
       </c>
       <c r="F21" t="n">
-        <v>7.8348</v>
+        <v>6.195499999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>-10.5915</v>
+        <v>-17.4914</v>
       </c>
       <c r="H21" t="n">
-        <v>2.2367</v>
+        <v>8.602199999999998</v>
       </c>
       <c r="I21" t="n">
-        <v>-12.8282</v>
+        <v>-26.0942</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.871200000000001</v>
+        <v>19.544</v>
       </c>
       <c r="K21" t="n">
-        <v>11.8821</v>
+        <v>35.3075</v>
       </c>
       <c r="L21" t="n">
-        <v>-13.7534</v>
+        <v>-15.7635</v>
       </c>
       <c r="M21" t="n">
-        <v>-8.7203</v>
+        <v>-37.0356</v>
       </c>
       <c r="N21" t="n">
-        <v>-9.6456</v>
+        <v>-26.7055</v>
       </c>
       <c r="O21" t="n">
-        <v>0.9250000000000003</v>
+        <v>-10.3304</v>
       </c>
       <c r="P21" t="n">
-        <v>-8.613300000000001</v>
+        <v>-17.4095</v>
       </c>
       <c r="Q21" t="n">
-        <v>-36.4682</v>
+        <v>-64.5065</v>
       </c>
       <c r="R21" t="n">
-        <v>27.855</v>
+        <v>47.0971</v>
       </c>
       <c r="S21" t="n">
-        <v>-17.0531</v>
+        <v>6.6732</v>
       </c>
       <c r="T21" t="n">
-        <v>-12.269</v>
+        <v>-2.7832</v>
       </c>
       <c r="U21" t="n">
-        <v>-4.7843</v>
+        <v>9.4565</v>
       </c>
       <c r="V21" t="n">
-        <v>10.3499</v>
+        <v>3.979800000000001</v>
       </c>
       <c r="W21" t="n">
-        <v>16.8654</v>
+        <v>17.3018</v>
       </c>
       <c r="X21" t="n">
-        <v>-6.515599999999999</v>
+        <v>-13.3222</v>
       </c>
     </row>
     <row r="22">
@@ -2125,22 +2125,22 @@
         <v>25</v>
       </c>
       <c r="D22" t="n">
-        <v>-71.27690000000001</v>
+        <v>-36.91430000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>-75.33510000000001</v>
+        <v>-64.04850000000002</v>
       </c>
       <c r="F22" t="n">
-        <v>4.058400000000002</v>
+        <v>27.13479999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.5460000000000029</v>
+        <v>-0.5460000000000065</v>
       </c>
       <c r="H22" t="n">
         <v>-12.0942</v>
       </c>
       <c r="I22" t="n">
-        <v>11.54639999999999</v>
+        <v>11.54640000000001</v>
       </c>
       <c r="J22" t="n">
         <v>211.79</v>
@@ -2170,16 +2170,16 @@
         <v>346.3564</v>
       </c>
       <c r="S22" t="n">
-        <v>-17.6816</v>
+        <v>16.6815</v>
       </c>
       <c r="T22" t="n">
-        <v>-39.0949</v>
+        <v>-27.809</v>
       </c>
       <c r="U22" t="n">
-        <v>21.41229999999999</v>
+        <v>44.4899</v>
       </c>
       <c r="V22" t="n">
-        <v>3.760399999999995</v>
+        <v>3.760399999999998</v>
       </c>
       <c r="W22" t="n">
         <v>155.1336</v>
